--- a/data/csv/way_point.xlsx
+++ b/data/csv/way_point.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\FrameWork\data\csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ytats\Desktop\FrameWork\data\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7C85A0-38B5-4BE4-9C6A-0744A1F2BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAF0A46-8013-4112-8011-A051C4D4F2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4056" yWindow="1908" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1875" yWindow="3525" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
@@ -96,8 +95,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -379,10 +381,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -399,7 +401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
@@ -416,7 +418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
@@ -436,7 +438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
@@ -456,7 +458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
@@ -476,7 +478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -492,7 +494,116 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-9.5399999999999991</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-72.849999999999994</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>115.7</v>
+      </c>
+      <c r="C8">
+        <v>-9.5500000000000007</v>
+      </c>
+      <c r="D8">
+        <v>-17.100000000000001</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>43.2</v>
+      </c>
+      <c r="C9">
+        <v>-9.5500000000000007</v>
+      </c>
+      <c r="D9">
+        <v>-24.24</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>-3.18</v>
+      </c>
+      <c r="C10">
+        <v>-9.5500000000000007</v>
+      </c>
+      <c r="D10">
+        <v>-28.28</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>-47.9</v>
+      </c>
+      <c r="C11">
+        <v>-9.5500000000000007</v>
+      </c>
+      <c r="D11">
+        <v>-26.9</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>-94.9</v>
+      </c>
+      <c r="C12">
+        <v>-9.5500000000000007</v>
+      </c>
+      <c r="D12">
+        <v>-13</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
